--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487134_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487134_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8397</v>
+        <v>7.4104</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4337</v>
+        <v>8.1114</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.594</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>6.6132</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2447</v>
+        <v>1.8154</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1991</v>
+        <v>0.8768</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0456</v>
+        <v>0.9386</v>
       </c>
       <c r="V2" t="n">
         <v>2.4559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5733</v>
+        <v>3.2649</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5483</v>
+        <v>3.2667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0249</v>
+        <v>-0.0018</v>
       </c>
       <c r="G3" t="n">
         <v>1.6197</v>
@@ -688,13 +688,13 @@
         <v>0.965</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1851</v>
+        <v>0.8768</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9479</v>
+        <v>0.6663</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2373</v>
+        <v>0.2105</v>
       </c>
       <c r="V3" t="n">
         <v>1.9264</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0649</v>
+        <v>1.5702</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4508</v>
+        <v>2.0096</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3859</v>
+        <v>-0.4395</v>
       </c>
       <c r="G4" t="n">
         <v>0.1846</v>
@@ -766,13 +766,13 @@
         <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1818</v>
+        <v>0.6871</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6954</v>
+        <v>0.2542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4865</v>
+        <v>0.4329</v>
       </c>
       <c r="V4" t="n">
         <v>0.6985</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ARRIBAS RODRIGUEZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2531</v>
+        <v>-0.3688</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0061</v>
+        <v>3.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2592</v>
+        <v>-3.4189</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0942</v>
+        <v>2.3885</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5516</v>
+        <v>-1.2338</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6458</v>
+        <v>3.6222</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3281</v>
+        <v>3.9769</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0828</v>
+        <v>0.0619</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2453</v>
+        <v>3.915</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2338</v>
+        <v>-1.5884</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6344</v>
+        <v>-1.2956</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4006</v>
+        <v>-0.2928</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.386</v>
+        <v>-1.5441</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-3.0881</v>
       </c>
       <c r="R5" t="n">
-        <v>0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0615</v>
+        <v>1.285</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3569</v>
+        <v>0.3616</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2954</v>
+        <v>0.9234</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8999</v>
+        <v>-2.4982</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.7997</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8999</v>
+        <v>-4.2979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>D. ARRIBAS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3133</v>
+        <v>-0.388</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7308</v>
+        <v>0.1657</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0441</v>
+        <v>-0.5537</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3885</v>
+        <v>1.0942</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2338</v>
+        <v>-0.5516</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6222</v>
+        <v>1.6458</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9769</v>
+        <v>1.3281</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0619</v>
+        <v>0.0828</v>
       </c>
       <c r="L6" t="n">
-        <v>3.915</v>
+        <v>1.2453</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5884</v>
+        <v>-0.2338</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2956</v>
+        <v>-0.6344</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2928</v>
+        <v>0.4006</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5441</v>
+        <v>-0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0881</v>
+        <v>-0.965</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3405</v>
+        <v>-0.1963</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0423</v>
+        <v>-0.1973</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2981</v>
+        <v>0.001</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.4982</v>
+        <v>-0.8999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.2979</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5653</v>
+        <v>-0.5128</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4592</v>
+        <v>-0.5405</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1061</v>
+        <v>0.0278</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5588</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4145</v>
+        <v>0.467</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3252</v>
+        <v>0.2439</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0892</v>
+        <v>0.2231</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8062</v>
+        <v>-0.5787</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0224</v>
+        <v>1.1428</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8286</v>
+        <v>-1.7215</v>
       </c>
       <c r="G8" t="n">
         <v>0.3649</v>
@@ -1078,13 +1078,13 @@
         <v>2.1231</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5222</v>
+        <v>0.7053</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1157</v>
+        <v>0.0047</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5935</v>
+        <v>0.7006</v>
       </c>
       <c r="V8" t="n">
         <v>-1.842</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2252</v>
+        <v>-2.0447</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6093</v>
+        <v>-1.5092</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6158</v>
+        <v>-0.5355</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6938</v>
@@ -1156,13 +1156,13 @@
         <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3034</v>
+        <v>-0.1229</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0535</v>
+        <v>0.1338</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9049</v>
+        <v>-3.0503</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3745</v>
+        <v>-1.0552</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5305</v>
+        <v>-1.9951</v>
       </c>
       <c r="G10" t="n">
         <v>-4.9804</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6544</v>
+        <v>0.2003</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2102</v>
+        <v>0.1091</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4442</v>
+        <v>0.0912</v>
       </c>
       <c r="V10" t="n">
         <v>0.5717</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.4099</v>
+        <v>5.302199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>13.7491</v>
+        <v>14.6413</v>
       </c>
       <c r="F11" t="n">
         <v>-9.3393</v>
@@ -1288,7 +1288,7 @@
         <v>20.3854</v>
       </c>
       <c r="K11" t="n">
-        <v>9.3499</v>
+        <v>9.349900000000002</v>
       </c>
       <c r="L11" t="n">
         <v>11.0355</v>
@@ -1303,7 +1303,7 @@
         <v>-4.2307</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.860199999999999</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q11" t="n">
         <v>-14.4755</v>
@@ -1312,22 +1312,22 @@
         <v>10.6154</v>
       </c>
       <c r="S11" t="n">
-        <v>4.825100000000001</v>
+        <v>5.717700000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1702</v>
+        <v>2.0625</v>
       </c>
       <c r="U11" t="n">
-        <v>3.6549</v>
+        <v>3.6551</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4123999999999991</v>
+        <v>0.4123999999999995</v>
       </c>
       <c r="W11" t="n">
         <v>6.6693</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.256800000000001</v>
+        <v>-6.2568</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.3877</v>
+        <v>5.4746</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0282</v>
+        <v>5.9281</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6405</v>
+        <v>-0.4535</v>
       </c>
       <c r="G12" t="n">
         <v>2.9472</v>
@@ -1390,13 +1390,13 @@
         <v>0.965</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1547</v>
+        <v>0.2416</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1322</v>
+        <v>0.0321</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0225</v>
+        <v>0.2095</v>
       </c>
       <c r="V12" t="n">
         <v>1.5138</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>J. ARRIAZU ARBIZU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2001</v>
+        <v>0.8337</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0939</v>
+        <v>2.0865</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8938</v>
+        <v>-1.2528</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6835</v>
+        <v>-0.4341</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.6073</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1235</v>
+        <v>-2.0414</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2929</v>
+        <v>1.9146</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5767</v>
+        <v>1.9146</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7161999999999999</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6094</v>
+        <v>-2.3487</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7697</v>
+        <v>-0.3073</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8397</v>
+        <v>-2.0414</v>
       </c>
       <c r="P13" t="n">
-        <v>0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>1.864</v>
+        <v>-0.1302</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5996</v>
+        <v>-0.3539</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2644</v>
+        <v>0.2237</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9264</v>
+        <v>2.1701</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.6406</v>
+        <v>2.4559</v>
       </c>
       <c r="X13" t="n">
         <v>-0.2859</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ARRIAZU ARBIZU</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5336</v>
+        <v>0.8096</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7861</v>
+        <v>1.6527</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2525</v>
+        <v>-0.8431</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4341</v>
+        <v>1.3774</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6073</v>
+        <v>1.1396</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.0414</v>
+        <v>0.2378</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9146</v>
+        <v>3.5191</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9146</v>
+        <v>2.1682</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.3509</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3487</v>
+        <v>-2.1418</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3073</v>
+        <v>-1.0286</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0414</v>
+        <v>-1.1132</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R14" t="n">
-        <v>1.158</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4303</v>
+        <v>-0.6716</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6544</v>
+        <v>-0.6891</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2241</v>
+        <v>0.0175</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1701</v>
+        <v>-2.2123</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4559</v>
+        <v>-0.9843</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2859</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1757</v>
+        <v>-0.0352</v>
       </c>
       <c r="E15" t="n">
-        <v>1.152</v>
+        <v>-0.0052</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3774</v>
+        <v>-0.8773</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1396</v>
+        <v>0.0767</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2378</v>
+        <v>-0.9539</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5191</v>
+        <v>0.1035</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1682</v>
+        <v>0.1035</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3509</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1418</v>
+        <v>-0.9808</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0286</v>
+        <v>-0.0268</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1132</v>
+        <v>-0.9539</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3161</v>
+        <v>0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.193</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>0.965</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3055</v>
+        <v>-0.1229</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1898</v>
+        <v>-0.1087</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1157</v>
+        <v>-0.0142</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.2123</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.9843</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0514</v>
+        <v>-0.3896</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2952</v>
+        <v>0.6919</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2438</v>
+        <v>-1.0815</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8773</v>
+        <v>0.6835</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0767</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9539</v>
+        <v>-0.1235</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1035</v>
+        <v>3.2929</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1035</v>
+        <v>2.5767</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9808</v>
+        <v>-2.6094</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0268</v>
+        <v>-1.7697</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9539</v>
+        <v>-0.8397</v>
       </c>
       <c r="P16" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R16" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0363</v>
+        <v>0.2743</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1917</v>
+        <v>0.1977</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.228</v>
+        <v>0.0766</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.9264</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-1.6406</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4626</v>
+        <v>-0.4358</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4626</v>
+        <v>-0.4358</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4805</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0178</v>
+        <v>0.0446</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6726</v>
+        <v>-0.6704</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2412</v>
+        <v>-0.9506</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4314</v>
+        <v>0.2802</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.079</v>
+        <v>-0.3507</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6477</v>
+        <v>1.388</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4313</v>
+        <v>-1.7386</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1717</v>
+        <v>1.6581</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2938</v>
+        <v>2.8306</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1221</v>
+        <v>-1.1724</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9073</v>
+        <v>-2.0088</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3539</v>
+        <v>-1.4426</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5534</v>
+        <v>-0.5662</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.0881</v>
       </c>
       <c r="R18" t="n">
-        <v>0.386</v>
+        <v>2.3161</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2076</v>
+        <v>-0.7756999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2974</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08989999999999999</v>
+        <v>-0.0271</v>
       </c>
       <c r="V18" t="n">
         <v>1.228</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9091</v>
+        <v>-0.6726</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0633</v>
+        <v>-0.2412</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1542</v>
+        <v>-0.4314</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4813</v>
+        <v>-2.079</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1863</v>
+        <v>-1.6477</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6676</v>
+        <v>-0.4313</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0207</v>
+        <v>-1.1717</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0207</v>
+        <v>-1.2938</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4606</v>
+        <v>-0.9073</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.207</v>
+        <v>-0.3539</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6676</v>
+        <v>-0.5534</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.772</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.193</v>
+        <v>0.386</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3325</v>
+        <v>-0.2076</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.119</v>
+        <v>-0.2974</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2135</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.144</v>
+        <v>-0.8288</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4513</v>
+        <v>-1.0633</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3073</v>
+        <v>0.2346</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3507</v>
+        <v>0.4813</v>
       </c>
       <c r="H20" t="n">
-        <v>1.388</v>
+        <v>-0.1863</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7386</v>
+        <v>0.6676</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6581</v>
+        <v>0.0207</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8306</v>
+        <v>0.0207</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1724</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0088</v>
+        <v>0.4606</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4426</v>
+        <v>-0.207</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5662</v>
+        <v>0.6676</v>
       </c>
       <c r="P20" t="n">
         <v>-0.772</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0881</v>
+        <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3161</v>
+        <v>0.193</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2493</v>
+        <v>-0.2522</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2492</v>
+        <v>-0.119</v>
       </c>
       <c r="U20" t="n">
-        <v>-0</v>
+        <v>-0.1332</v>
       </c>
       <c r="V20" t="n">
-        <v>1.228</v>
+        <v>-0.2859</v>
       </c>
       <c r="W20" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6948</v>
+        <v>-1.0933</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1332</v>
+        <v>2.3335</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.828</v>
+        <v>-3.4268</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2409</v>
@@ -2092,13 +2092,13 @@
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.396</v>
+        <v>-0.7945</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8328</v>
+        <v>-0.6325</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5632</v>
+        <v>-0.162</v>
       </c>
       <c r="V21" t="n">
         <v>0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7463</v>
+        <v>-2.586</v>
       </c>
       <c r="E22" t="n">
         <v>0.3155</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0618</v>
+        <v>-2.9015</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9962</v>
@@ -2170,13 +2170,13 @@
         <v>1.3511</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1011</v>
+        <v>0.0592</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1057</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0046</v>
+        <v>0.1649</v>
       </c>
       <c r="V22" t="n">
         <v>-1.842</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1289</v>
+        <v>-3.4808</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7091</v>
+        <v>-1.4087</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4198</v>
+        <v>-2.0721</v>
       </c>
       <c r="G23" t="n">
         <v>-2.0628</v>
@@ -2248,13 +2248,13 @@
         <v>1.9301</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8032</v>
+        <v>-1.1551</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1303</v>
+        <v>-0.8298</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3252</v>
       </c>
       <c r="V23" t="n">
         <v>-1.228</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.409800000000001</v>
+        <v>-3.0746</v>
       </c>
       <c r="E24" t="n">
-        <v>9.339200000000002</v>
+        <v>9.339199999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.749</v>
+        <v>-12.4137</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0321</v>
@@ -2305,7 +2305,7 @@
         <v>13.1225</v>
       </c>
       <c r="L24" t="n">
-        <v>4.230699999999999</v>
+        <v>4.2307</v>
       </c>
       <c r="M24" t="n">
         <v>-20.3853</v>
@@ -2326,16 +2326,16 @@
         <v>14.4755</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.8253</v>
+        <v>-3.4901</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.6551</v>
+        <v>-3.6548</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.17</v>
+        <v>0.165</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.4125999999999996</v>
+        <v>-0.4125999999999992</v>
       </c>
       <c r="W24" t="n">
         <v>6.2567</v>
